--- a/r5-core-main/all-profiles.xlsx
+++ b/r5-core-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-16T09:04:28+00:00</t>
+    <t>2024-10-26T11:58:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -17117,7 +17117,7 @@
         <v>76</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>23</v>

--- a/r5-core-main/all-profiles.xlsx
+++ b/r5-core-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T12:32:55+00:00</t>
+    <t>2024-10-26T13:09:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/all-profiles.xlsx
+++ b/r5-core-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T13:28:10+00:00</t>
+    <t>2024-10-26T14:16:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/all-profiles.xlsx
+++ b/r5-core-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T20:47:41+00:00</t>
+    <t>2024-11-17T21:11:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/all-profiles.xlsx
+++ b/r5-core-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T21:35:06+00:00</t>
+    <t>2024-11-27T13:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/all-profiles.xlsx
+++ b/r5-core-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-27T13:18:58+00:00</t>
+    <t>2024-12-15T14:03:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1608,10 +1608,10 @@
     <t>Organization.identifier:KANR.system</t>
   </si>
   <si>
-    <t>OID for the Austrian Federal Ministry of Health</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.40.0.34.3.1.1</t>
+    <t>OID for the Krankenanstaltennummer (KA-Nr) in Austria</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.40.0.34.4.10</t>
   </si>
   <si>
     <t>Organization.identifier:KANR.value</t>

--- a/r5-core-main/all-profiles.xlsx
+++ b/r5-core-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-15T14:03:14+00:00</t>
+    <t>2024-12-19T08:32:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -53596,7 +53596,7 @@
         <v>76</v>
       </c>
       <c r="H438" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I438" t="s" s="2">
         <v>23</v>

--- a/r5-core-main/all-profiles.xlsx
+++ b/r5-core-main/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-08T14:32:12+00:00</t>
+    <t>2025-01-24T13:05:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/all-profiles.xlsx
+++ b/r5-core-main/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T13:05:30+00:00</t>
+    <t>2025-01-24T15:13:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/all-profiles.xlsx
+++ b/r5-core-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T15:13:16+00:00</t>
+    <t>2025-01-27T12:15:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/all-profiles.xlsx
+++ b/r5-core-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-27T09:10:20+00:00</t>
+    <t>2026-03-01T19:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/all-profiles.xlsx
+++ b/r5-core-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:31:53+00:00</t>
+    <t>2026-07-17T05:18:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
